--- a/Result/checksun_type/監視器_顯示器.xlsx
+++ b/Result/checksun_type/監視器_顯示器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>11.91</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>11.92</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>67153.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4856013.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4856013.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2669055.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2569084.76</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2569084.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-99372.99614899745</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>67153</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>67153.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>11.94</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>93192.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4882081.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4882081.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2812982.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2573541.14</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2573541.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>155381.013016066</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>93192</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>93192.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>11.97</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6386374.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4926629.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>4926629.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2837272.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2577261.02</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2577261.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>510976.0970727261</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6386374</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6386374.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>11.98</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>342597.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3771104.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3771104.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2215460.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2451844.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2451844.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>326450.4279725007</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>342597</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>342597.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>11.99</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>17390751.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3865654.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>3865654.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2222042.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2447349.84</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2447349.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>698730.9211160173</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>17390751</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>17390751.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>197495.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>482097.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>482097.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>500236.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2103473.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2103473.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-620982.4072902447</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>197495</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>197495.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>12.02</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>315931.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>743883.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>743883.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>497838.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2102718.46</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2102718.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-641974.6476102534</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>315931</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>315931.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>12.01</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>608749.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>747915.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>747915</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>474162.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2101152.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2101152.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-661725.4677956139</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>608749</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>608749.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>11.97</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>815348.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>659815.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>659815.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>425837.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2091685.8</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2091685.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-697681.2299248572</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>815348</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>815348.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>11.93</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>472964.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>578429.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>578429.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>367266.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2080978.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2080978.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-746265.0247550311</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>472964</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>472964.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>11.91</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>11.92</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11.94</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1506427.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>518375.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>518375.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>360403.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2076618.72</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2076618.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-752334.1236283141</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1506427</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1506427.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>10.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>6305887.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>7393258.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>7393258.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10517267.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>20568071.26</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>20568071.26</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1787012.246778358</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>6305887</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>6305887.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>10.21</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>6730463.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>8143750.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>8143750.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10751948.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>20786752.56</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>20786752.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1731711.459589692</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>6730463</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>6730463.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>8188113.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>10252271.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>10252271.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>11380459.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>21012264.76</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>21012264.76</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1636353.782906249</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>8188113</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>8188113.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>10.27</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>11.26</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11.26</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>9675415.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>12157509.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>12157509.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>11738500.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>21280071.54</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>21280071.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1597864.109683253</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>9675415</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>9675415.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>10.43</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>11.28</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11.28</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>6066413.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>12520435.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>12520435.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>11198491.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>21364951.88</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>21364951.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1645166.072590286</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>6066413</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>6066413.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>10.65</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11.3</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>10058347.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>13641276.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>13641276.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>11429840.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>21624569.6</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>21624569.6</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1267305.588436393</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>10058347</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>10058347.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>11.32</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>17273069.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>13360147.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>13360147</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>11469505.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>21758890.56</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>21758890.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1109951.197200963</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>17273069</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>17273069.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>17714305.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>12508646.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>12508646.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>10959217.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>21599596.86</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>21599596.86</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1618524.024107456</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>17714305</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>17714305.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>11.38</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>11490043.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>11319491.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>11319491.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>10877105.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>21406229.02</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>21406229.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-2334527.490255751</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>11490043</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>11490043.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>11.14</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>11.46</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>11670618.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>9876547.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>9876547.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>11219565.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>21593346.16</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>21593346.16</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-2607128.38867275</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>11670618</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>11670618.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>11.16</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>11.51</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8652700.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9218405.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9218405</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>12205749.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>21688059.2</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>21688059.2</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-2922793.836815866</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8652700</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8652700.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>80.32000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>83.76</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>83.76000000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6154.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>11416.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>11416</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>14200.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>19092.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>19092.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-2276.381225536164</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6154</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6154.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>79.82</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>83.32</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>83.95</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>83.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>7843.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>13837.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>13837.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>17431.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>19372.7</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>19372.7</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1847.58152362209</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7843</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7843.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>79.88</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>83.48</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>84.18</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>84.18000000000001</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>9429.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>17352.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>17352.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>19005.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>19449.8</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>19449.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1349.98975218691</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>9429</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>9429.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>80.98</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>83.71</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>84.41</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>84.41</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>12303.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>17354.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>17354</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>19326.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>19488.74</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>19488.74</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-760.8590161299762</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>12303</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>12303.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>81.96000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>84.68</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>84.68000000000001</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>21351.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>17917.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>17917.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>19846.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>19569.2</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>19569.2</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-199.9987140439989</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>21351</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>21351.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>82.96000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>84.3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>84.92</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>84.92</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>18262.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>16985.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>16985.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>20408.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>19515.22</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>19515.22</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-361.055471276748</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>18262</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>18262.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>84.48</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>84.84</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>85.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>25418.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>21026.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>21026</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>22200.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>20361.92</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>20361.92</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-247.277429063648</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>25418</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>25418.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>85.18</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>85.47</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>85.47</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9436.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>20658.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>20658.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>22253.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>20413.76</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>20413.76</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-842.6203177212301</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9436</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9436.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>85.22</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>85.06</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>85.63</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>85.63</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>15121.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>21299.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>21299.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>23448.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21080.66</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21080.66</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>49.34056697226697</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>15121</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>15121.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>85.38</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>85.8</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>85.8</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>16690.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>21775.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>21775.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>23259.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21155.18</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21155.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>712.7010962853965</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>16690</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>16690.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>85.42</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>84.87</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>85.95</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>85.95</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>38465.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>23831.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>23831</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>22246.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21400.92</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21400.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1466.798241865392</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>38465</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>38465.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>40.79</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>42.49</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>44.58</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>44.58</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4102.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2757.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2757.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3670.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2178.26</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2178.26</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>58.73819963476308</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4102</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4102.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.86</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>42.65</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>44.71</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>44.71</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>3586.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2755.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2755.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3432.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2129.54</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2129.54</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-5.025251621802454</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>3586</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>3586.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>40.92</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>42.82</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>44.84</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1988.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3256.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3256.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3575.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2072.16</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2072.16</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-40.65070871611761</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1988</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1988.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>40.96</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>44.99</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>44.99</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3041.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3567.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3567.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3604.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2036.44</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2036.44</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>81.12187788900792</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3041</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3041.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>41.16</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>43.16</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>45.13</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>45.13</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1071.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>4580.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>4580.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3634.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1994.96</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1994.96</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>139.3640774002943</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1071</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1071.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>41.65000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>43.33</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>45.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>45.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4093.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4583.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4583.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>4024.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1978.44</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1978.44</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>428.6613596521215</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4093</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4093.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>42.12</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>45.42</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>45.42</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6088.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4110.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4110</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>4006.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1897.56</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1897.56</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>502.8481428814416</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6088</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6088.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>43.72</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>45.57</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>3545.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3894.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3894.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3919.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1788.38</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1788.38</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>377.1203995347046</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>3545</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>3545.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>43.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>45.72</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>45.72</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>8106.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3640.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3640.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3860.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1742.88</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1742.88</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>456.5050376274121</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>8106</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>8106.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>43.59</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>44.14</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>45.85</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1085.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2688.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2688.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>3475.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1592.36</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1592.36</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>64.92934070172942</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1085</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1085.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>43.63</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1726.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3465.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3465.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3502.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1578.56</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1578.56</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>255.4665829256933</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1726</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1726.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>23.57</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>24.98</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>24.98</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>595.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>590.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>590.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>680.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1093.86</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1093.86</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-99.31783420592717</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>595</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>23.5</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>23.84</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>25.02</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>25.02</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>200.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>598.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>598.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>697.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1116.88</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1116.88</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-103.9491901489453</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>200</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>23.5</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>25.08</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1074.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>734.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>734.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>847.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1147.04</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1147.04</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-64.53151327650903</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1074</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1074.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>23.52</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>25.15</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>861.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>619.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>619.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>860.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1147.18</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1147.18</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-99.55870655601029</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>861</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>861.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>23.57</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>25.21</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>222.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>624.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>624.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>891.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1151.52</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1151.52</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-123.2204574354405</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>222</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>222.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>23.56</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>25.28</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>25.28</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>635.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>770.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>770.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1122.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1161.18</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1161.18</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-84.15794235478916</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>635</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>635.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>23.59</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>25.35</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>880.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>796.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>796.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1113.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1163.82</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1163.82</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-69.59870858404474</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>880</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>880.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>23.59</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>25.42</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>501.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>959.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>959.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1034.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1174.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1174.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-72.56413503355122</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>501</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>501.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>23.61</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>25.49</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>883.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1100.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1100.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1009.7</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1196.5</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1196.5</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-33.60173942450501</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>883</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>883.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>23.64</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>25.56</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>954.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1158.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1158.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1015.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1195.92</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1195.92</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-17.66968357499263</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>954</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>954.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>23.72</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>764.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1474.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1474.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1128.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1208.52</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1208.52</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-1.885686519439332</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>764</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>764.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>31.51</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>32.81</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>33.47</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>33.47</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>5320.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>8434.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>8434.799999999999</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>8195.7</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>10060.92</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>10060.92</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-225.0112371728083</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>5320</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>5320.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>31.38</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>33.51</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>33.51</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>6014.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>8764.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>8764.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>8189.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>10586.72</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>10586.72</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>44.02321701557048</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>6014</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>6014.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>31.48</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>33.1</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>33.6</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>7662.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>11755.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>11755.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>9147.8</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>11714.54</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>11714.54</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>352.4287509626993</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>7662</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>7662.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>31.86</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>33.28</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>33.68</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>33.68</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>18551.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>11111.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>11111.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>9097.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>11782.96</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>11782.96</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>603.8499154956426</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>18551</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>18551.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>33.76</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>4627.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>8003.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>8003.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>7841.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>11815.02</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>11815.02</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-225.221632153567</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>4627</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>4627.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>33.59</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>33.84</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6969.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>7956.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>7956.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>8204.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>12383.68</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>12383.68</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>90.29121521018897</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6969</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6969.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>33.74</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>33.95</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>33.95</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>20967.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>7614.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>7614.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>8229.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>12809.46</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>12809.46</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>286.8705966151938</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>20967</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>20967.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>33.9</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>34.08</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>4444.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>6540.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>6540.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>6818.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>12972.68</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>12972.68</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-942.332808399633</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>4444</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>4444.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>33.76000000000001</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>33.89</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>34.28</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>3011.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>7083.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>7083.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>6775.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>13311.1</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>13311.1</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-894.3615009779678</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>3011</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>3011.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>33.56</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>33.86</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>34.48</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>34.48</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>4392.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>7679.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>7679.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>7426.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>13576.66</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>13576.66</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-640.3538653406604</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>4392</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>4392.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>33.41</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>34.67</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>34.67</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>5259.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>8452.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>8452</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>7631.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>13998.28</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>13998.28</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-402.5803192394833</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>5259</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>5259.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>26.64</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>29.76</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>29.76</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>12947.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>26318.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>26318.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>16294.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>14302.9</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>14302.9</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>2116.636459194189</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>12947</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>12947.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>26.39</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>29.96</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>7393.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>24633.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>24633.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>15669.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>20401.14</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>20401.14</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>2926.220914931811</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>7393</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>7393.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>26.35</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>27.64</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>30.15</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>24831.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>24790.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>24790</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>15333.6</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>22624.02</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>22624.02</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>4573.333676166567</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>24831</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>24831.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>30.27</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>30.27</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>79020.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>21051.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>21051.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>13345.3</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>22455.72</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>22455.72</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>4894.661418067404</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>79020</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>79020.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>26.68</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>30.4</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>7400.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>6357.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>6357.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>5915.9</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>21217.42</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>21217.42</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-627.0725727195168</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>7400</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>7400.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>26.96</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>28.09</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>30.52</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>4522.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>6271.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>6271.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>6117.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>21387.62</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>21387.62</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-819.2971105322777</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>4522</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>4522.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>27.4</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>28.29</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>30.66</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>30.66</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>8177.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>6705.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>6705.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>6223.4</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>22101.32</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>22101.32</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-756.2858391743566</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>8177</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>8177.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>27.71</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>30.8</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>6140.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>5877.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>5877.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>6394.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>22506.0</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>22506</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-1030.866671549668</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>6140</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>6140.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>27.82</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>30.92</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>30.92</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>5550.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>5638.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>5638.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>6264.0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>23529.66</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>23529.66</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-1168.058336673341</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>5550</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>5550.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>27.87</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>31.07</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>31.07</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>6969.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>5474.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>5474</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>6321.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>24230.9</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>24230.9</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-1259.115774825967</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>6969</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>6969.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>27.84</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>31.24</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>6692.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>5963.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>5963</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>6185.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>24863.82</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>24863.82</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-1496.265123085936</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>6692</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>6692.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>10.208</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>11.96</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>11.96</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>9688964.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>14416758.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>14416758</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>11926081.2</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>15053754.92</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>15053754.92</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>94678.83287869208</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>9688964</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>9688964.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>10.148</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>12.01</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>10263509.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>15386175.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>15386175</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>11609683.5</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>15092603.28</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>15092603.28</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>357788.3151826318</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>10263509</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>10263509.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>10.258</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>12.07</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>11276785.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>15561990.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>15561990.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>11157913.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>15141244.42</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>15141244.42</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>659322.457217453</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>11276785</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>11276785.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>10.428</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>12.14</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>19143857.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>15473930.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>15473930.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>10732644.0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>15166545.86</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>15166545.86</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>957973.0009380039</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>19143857</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>19143857.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>10.65</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>12.21</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>12.21</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>21710675.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>12711860.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>12711860</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>9357895.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>15316885.62</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>15316885.62</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>507502.7419338617</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>21710675</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>21710675.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>11.18</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>12.28</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>14536049.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>9435404.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>9435404.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>7737781.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>15395033.68</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>15395033.68</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-429167.5117125474</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>14536049</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>14536049.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>11.05</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>12.34</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>11142587.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>7833192.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>7833192</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>7420859.3</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>15727339.84</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>15727339.84</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-983230.5343605429</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>11142587</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>11142587.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>11.11</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>11.31</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>12.38</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>10836486.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>6753836.6</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>6753836.6</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>7637186.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>15673797.04</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>15673797.04</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-1376048.547630519</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>10836486</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>10836486.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>11.13</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>11.36</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>12.41</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>5333503.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>5991357.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>5991357.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>7416006.4</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>15596153.94</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>15596153.94</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-1855276.011315107</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>5333503</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>5333503.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>11.13</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>12.45</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>5328397.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>6003931.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>6003931.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>10258374.7</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>15717602.9</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>15717602.9</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-1884021.494746122</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>5328397</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>5328397.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>11.11</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>11.44</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>12.48</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>12.48</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>6524987.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>6040158.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>6040158.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>10316398.2</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>15845844.58</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>15845844.58</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-1857252.917692354</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>6524987</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>6524987.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>14.61</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>14.4</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>24936838.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>30822043.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>30822043.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>46911445.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>51199805.14</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>51199805.14</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-3733685.064264968</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>24936838</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>24936838.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>14.46</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>14.37</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>14.37</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>20889696.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>36972173.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>36972173.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>49665121.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>51154306.6</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>51154306.6</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-2966680.800394706</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>20889696</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>20889696.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>14.72</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>14.34</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>40243435.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>45102521.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>45102521.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>51152191.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>51161794.86</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>51161794.86</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-1331385.180565961</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>40243435</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>40243435.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>14.33</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>35613427.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>44406342.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>44406342.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>50606982.4</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>50966314.28</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>50966314.28</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-1021314.002933256</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>35613427</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>35613427.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>14.31</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>14.31</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>32426823.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>46111197.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>46111197</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>51294892.3</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>50812570.52</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>50812570.52</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-45807.39192461967</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>32426823</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>32426823.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>15.1</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>14.59</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>14.3</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>55687485.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>63000846.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>63000846.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>51963178.8</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>50792076.3</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>50792076.3</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>1690831.316370726</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>55687485</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>55687485.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>14.28</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>61541437.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>62358069.8</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>62358069.8</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>48454781.8</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>51591368.42</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>51591368.42</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>1619143.138350844</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>61541437</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>61541437.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>14.62</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>14.24</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>36762540.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>57201861.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>57201861.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>45697674.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>50766311.38</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>50766311.38</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>831695.7719527707</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>36762540</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>36762540.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>14.66</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>14.21</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>44137700.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>56807622.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>56807622.4</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>44049880.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>50729203.92</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>50729203.92</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>2331949.363814346</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>44137700</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>44137700.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>14.38</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>14.17</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>116875070.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>56478587.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>56478587.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>42013498.2</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>50276522.96</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>50276522.96</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>3601689.160623237</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>116875070</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>116875070.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>14.15</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>14.13</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>52473602.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>40925511.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>40925511.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>34675123.2</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>48640844.18</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>48640844.18</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-2506318.242529176</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>52473602</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>52473602.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>403535423</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>363440217</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>451484020</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>569640781</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>1056628890</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>436450840</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>365688993</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>676579414</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>622810797</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>566992376</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>832928036</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>30.33</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>90130496.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>102891471.6</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>102891471.6</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>139976545.9</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>162929477.08</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>162929477.08</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-8302235.025979221</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>90130496</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>90130496.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>26.99</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>30.41</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>116543934.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>110660624.8</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>110660624.8</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>154792338.5</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>167930362.34</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>167930362.34</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-6234570.233193085</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>116543934</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>116543934.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>26.85</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>30.48</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>30.48</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>105477076.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>123333532.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>123333532.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>155136214.6</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>169872793.4</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>169872793.4</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-5888111.378027424</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>105477076</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>105477076.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>29.58</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>30.55</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>106737599.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>132241859.8</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>132241859.8</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>153400791.7</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>175800706.34</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>175800706.34</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-3997145.678575486</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>106737599</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>106737599.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>27.16</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>30.65</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>95568253.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>148004191.6</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>148004191.6</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>154119988.6</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>183315477.76</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>183315477.76</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-1288066.94083789</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>95568253</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>95568253.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>30.76</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>128976262.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>177061620.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>177061620.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>155197777.5</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>212132753.64</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>212132753.64</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>3824763.575245768</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>128976262</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>128976262.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>27.75</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>30.85</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>179908472.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>198924052.2</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>198924052.2</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>151303002.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>221958679.64</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>221958679.64</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>7412778.934820741</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>179908472</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>179908472.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>28.34</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>30.51</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>30.94</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>150018713.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>186938896.8</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>186938896.8</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>144140116.0</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>249744552.38</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>249744552.38</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>6816750.557969987</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>150018713</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>150018713.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>28.82</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>30.68</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>31.06</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>185549258.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>174559723.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>174559723.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>137660190.9</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>308682445.76</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>308682445.76</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>8924300.249684244</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>185549258</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>185549258.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>240855396.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>160235785.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>160235785.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>132464211.4</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>323808057.5</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>323808057.5</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>7809516.407501608</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>240855396</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>240855396.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>31.1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>238288422.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>133333934.8</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>133333934.8</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>124708175.2</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>321307698.24</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>321307698.24</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>12399.11840137839</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>238288422</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>238288422.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>34.28</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>703729.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>832338.4</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>832338.4</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>1365486.3</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>2770195.72</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>2770195.72</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-407242.1677682393</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>703729</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>703729.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>34.05</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>34.34</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>811272.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>1025107.0</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>1025107</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>1422951.5</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>2781982.36</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>2781982.36</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-397836.2898797004</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>811272</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>811272.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>34.42</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>35.78</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>35.78</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>1487179.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>1339575.6</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>1339575.6</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>1890505.4</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-381713.3468289413</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>1487179</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>1487179.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>35.84</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>582054.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>1655590.0</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>1655590</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>2092838.2</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>2769787.1</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>2769787.1</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-417466.5586553942</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>582054</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>582054.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>33.92999999999999</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>34.57</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>577458.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>1688519.2</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>1688519.2</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>2334206.6</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>2765629.48</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>2765629.48</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-356655.3770269202</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>577458</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>577458.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>33.93</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>35.97</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>35.97</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>1667572.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>1898634.2</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>1898634.2</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>2466923.8</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>2771121.32</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>2771121.32</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-256552.1398067102</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>1667572</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>1667572.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>33.97</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>36.03</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>36.03</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>2383615.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>1820796.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>1820796</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>2506266.8</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>2754839.88</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>2754839.88</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-221182.8673561704</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>2383615</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>2383615.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>34.83</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>3067251.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>2441435.2</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>2441435.2</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>2486763.3</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>2745284.78</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>2745284.78</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-239474.8400212508</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>3067251</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>3067251.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>33.98999999999999</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>36.15</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>746700.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>2530086.4</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>2530086.4</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>2848651.5</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>2788241.7</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>2788241.7</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-330300.2709706062</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>746700</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>746700.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>34.08</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>36.21</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>36.21</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>1628033.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>2979894.0</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>2979894</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>3115544.6</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>2857333.8</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>2857333.8</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-199623.9840778778</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>1628033</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>1628033.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>34.17</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>36.27</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>36.27</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>1278381.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>3035213.4</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>3035213.4</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>3208352.2</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>2902801.48</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>2902801.48</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-100242.6819426282</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>1278381</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>1278381.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
